--- a/exports/trend_1d/IRFC_full_report.xlsx
+++ b/exports/trend_1d/IRFC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>9.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H2" t="n">
-        <v>23.8</v>
+        <v>23.45</v>
       </c>
       <c r="I2" t="n">
         <v>23.67562842678594</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.3</v>
+        <v>-7.68</v>
       </c>
       <c r="L2" t="n">
-        <v>7.48</v>
+        <v>7.87</v>
       </c>
       <c r="M2" t="n">
         <v>2.32</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H3" t="n">
-        <v>21.1</v>
+        <v>22.55</v>
       </c>
       <c r="I3" t="n">
         <v>22.19040014151793</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K3" t="n">
-        <v>10.02</v>
+        <v>3.84</v>
       </c>
       <c r="L3" t="n">
         <v>1.92</v>
@@ -612,7 +647,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>6.87</v>
       </c>
       <c r="O3" t="n">
         <v>-1.47</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44390</v>
+        <v>44391</v>
       </c>
       <c r="H4" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I4" t="n">
         <v>23.63455865789023</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>4.21</v>
       </c>
       <c r="L4" t="n">
         <v>6.43</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H5" t="n">
-        <v>22.85</v>
+        <v>23.9</v>
       </c>
       <c r="I5" t="n">
         <v>23.1907623322083</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K5" t="n">
-        <v>2.77</v>
+        <v>-1.7</v>
       </c>
       <c r="L5" t="n">
         <v>3.19</v>
@@ -726,7 +785,7 @@
         <v>1.89</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>-0.84</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.19</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H6" t="n">
-        <v>23.7</v>
+        <v>23.35</v>
       </c>
       <c r="I6" t="n">
         <v>23.48231042560993</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.84</v>
+        <v>-2.3</v>
       </c>
       <c r="L6" t="n">
         <v>4.81</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>7.24</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H7" t="n">
-        <v>23.7</v>
+        <v>24.05</v>
       </c>
       <c r="I7" t="n">
         <v>23.76313333330331</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5</v>
+        <v>-3</v>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>3.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.87</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
         <v>3.04</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>4.55</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H8" t="n">
-        <v>23.3</v>
+        <v>22.85</v>
       </c>
       <c r="I8" t="n">
         <v>22.95630959589312</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.12</v>
+        <v>-4.99</v>
       </c>
       <c r="L8" t="n">
-        <v>3.33</v>
+        <v>5.41</v>
       </c>
       <c r="M8" t="n">
         <v>0.21</v>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
         <v>1.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H9" t="n">
-        <v>22.25</v>
+        <v>22.85</v>
       </c>
       <c r="I9" t="n">
         <v>22.49322002906734</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>3.28</v>
@@ -954,7 +1061,7 @@
         <v>1.52</v>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
         <v>-1.93</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H10" t="n">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="I10" t="n">
         <v>21.44015017437914</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.13</v>
+        <v>-6.35</v>
       </c>
       <c r="L10" t="n">
-        <v>6.56</v>
+        <v>7.22</v>
       </c>
       <c r="M10" t="n">
         <v>0.91</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H11" t="n">
-        <v>20.45</v>
+        <v>20.65</v>
       </c>
       <c r="I11" t="n">
         <v>20.46377530002047</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>4.44</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>2.57</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.31</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="I12" t="n">
         <v>21.92656512927136</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K12" t="n">
-        <v>6.54</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.94</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.14</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44859</v>
+        <v>44861</v>
       </c>
       <c r="H13" t="n">
-        <v>21.95</v>
+        <v>22.3</v>
       </c>
       <c r="I13" t="n">
         <v>22.02979971268512</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.62</v>
+        <v>-3.24</v>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>3.94</v>
       </c>
       <c r="M13" t="n">
         <v>3.07</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.29</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H14" t="n">
-        <v>31.25</v>
+        <v>27.85</v>
       </c>
       <c r="I14" t="n">
         <v>30.39615647643976</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K14" t="n">
-        <v>40.13</v>
+        <v>24.89</v>
       </c>
       <c r="L14" t="n">
         <v>1.12</v>
@@ -1239,7 +1406,7 @@
         <v>1.82</v>
       </c>
       <c r="N14" t="n">
-        <v>9.4</v>
+        <v>10.88</v>
       </c>
       <c r="O14" t="n">
         <v>1.59</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>30.14</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H15" t="n">
-        <v>27.55</v>
+        <v>28.25</v>
       </c>
       <c r="I15" t="n">
         <v>27.89289051412297</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K15" t="n">
-        <v>1.08</v>
+        <v>-1.44</v>
       </c>
       <c r="L15" t="n">
         <v>24.24</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.33</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H16" t="n">
-        <v>153.7</v>
+        <v>132.95</v>
       </c>
       <c r="I16" t="n">
         <v>139.9899909651227</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K16" t="n">
-        <v>444.07</v>
+        <v>370.62</v>
       </c>
       <c r="L16" t="n">
         <v>2.65</v>
@@ -1353,7 +1544,7 @@
         <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>8.48</v>
+        <v>13.5</v>
       </c>
       <c r="O16" t="n">
         <v>2.54</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>32.79</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45407</v>
+        <v>45408</v>
       </c>
       <c r="H17" t="n">
-        <v>150.25</v>
+        <v>158.05</v>
       </c>
       <c r="I17" t="n">
         <v>154.1254826466427</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" t="n">
-        <v>-13.01</v>
+        <v>-18.88</v>
       </c>
       <c r="L17" t="n">
         <v>23.62</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H18" t="n">
-        <v>192.27</v>
+        <v>183.56</v>
       </c>
       <c r="I18" t="n">
         <v>190.2575189309759</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>21.65</v>
+        <v>16.14</v>
       </c>
       <c r="L18" t="n">
         <v>9.869999999999999</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>22.91</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="H19" t="n">
-        <v>143.53</v>
+        <v>155.55</v>
       </c>
       <c r="I19" t="n">
         <v>151.7903023981958</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K19" t="n">
-        <v>21.81</v>
+        <v>15.26</v>
       </c>
       <c r="L19" t="n">
         <v>8.029999999999999</v>
@@ -1524,7 +1751,7 @@
         <v>3.03</v>
       </c>
       <c r="N19" t="n">
-        <v>6.73</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-4.53</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>16.45</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45610</v>
+        <v>45614</v>
       </c>
       <c r="H20" t="n">
-        <v>139.66</v>
+        <v>138.29</v>
       </c>
       <c r="I20" t="n">
         <v>138.7811612368894</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-10.22</v>
+        <v>-11.1</v>
       </c>
       <c r="L20" t="n">
-        <v>10.45</v>
+        <v>11.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.23</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>12.89</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H21" t="n">
-        <v>150.84</v>
+        <v>158</v>
       </c>
       <c r="I21" t="n">
         <v>156.1102745213508</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.08</v>
+        <v>-14.25</v>
       </c>
       <c r="L21" t="n">
-        <v>12.55</v>
+        <v>15.44</v>
       </c>
       <c r="M21" t="n">
         <v>4.82</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.41</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H22" t="n">
-        <v>148.41</v>
+        <v>147.79</v>
       </c>
       <c r="I22" t="n">
         <v>148.1676929993433</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.07</v>
+        <v>-6.46</v>
       </c>
       <c r="L22" t="n">
-        <v>6.33</v>
+        <v>7.03</v>
       </c>
       <c r="M22" t="n">
         <v>3.16</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.79</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="H23" t="n">
-        <v>141.73</v>
+        <v>148.23</v>
       </c>
       <c r="I23" t="n">
         <v>147.960750897222</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>-0.3</v>
       </c>
       <c r="L23" t="n">
         <v>6.91</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>13.14</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45695</v>
+        <v>45698</v>
       </c>
       <c r="H24" t="n">
-        <v>133.43</v>
+        <v>131.05</v>
       </c>
       <c r="I24" t="n">
         <v>132.4309452741201</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.98</v>
+        <v>-11.59</v>
       </c>
       <c r="L24" t="n">
-        <v>10.27</v>
+        <v>11.88</v>
       </c>
       <c r="M24" t="n">
         <v>2.75</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>13.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H25" t="n">
-        <v>128.11</v>
+        <v>128.52</v>
       </c>
       <c r="I25" t="n">
         <v>128.3484097656739</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K25" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="L25" t="n">
         <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="N25" t="n">
         <v>5.18</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H26" t="n">
-        <v>125.01</v>
+        <v>120.37</v>
       </c>
       <c r="I26" t="n">
         <v>122.3902657375553</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.73</v>
+        <v>-6.34</v>
       </c>
       <c r="L26" t="n">
         <v>12.08</v>
@@ -1923,7 +2234,7 @@
         <v>9.48</v>
       </c>
       <c r="N26" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="O26" t="n">
         <v>0.32</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>12.44</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="H27" t="n">
-        <v>124.76</v>
+        <v>129.96</v>
       </c>
       <c r="I27" t="n">
         <v>129.2254086486117</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.65</v>
+        <v>-7.97</v>
       </c>
       <c r="L27" t="n">
-        <v>4.76</v>
+        <v>8.23</v>
       </c>
       <c r="M27" t="n">
         <v>5.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H28" t="n">
-        <v>136.02</v>
+        <v>132.35</v>
       </c>
       <c r="I28" t="n">
         <v>135.2850613125395</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>4.66</v>
+        <v>1.84</v>
       </c>
       <c r="L28" t="n">
         <v>4.05</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.72</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H29" t="n">
-        <v>126.23</v>
+        <v>128.18</v>
       </c>
       <c r="I29" t="n">
         <v>126.5610617683555</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K29" t="n">
-        <v>4.62</v>
+        <v>3.15</v>
       </c>
       <c r="L29" t="n">
         <v>8.16</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.03</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H30" t="n">
-        <v>124.08</v>
+        <v>121.91</v>
       </c>
       <c r="I30" t="n">
         <v>122.6389549255571</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.2</v>
+        <v>-4.89</v>
       </c>
       <c r="L30" t="n">
-        <v>3.57</v>
+        <v>5.16</v>
       </c>
       <c r="M30" t="n">
         <v>0.34</v>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="O30" t="n">
         <v>1.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.92</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="H31" t="n">
-        <v>117</v>
+        <v>121.4</v>
       </c>
       <c r="I31" t="n">
         <v>117.3656568120688</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="n">
-        <v>4.03</v>
+        <v>0.42</v>
       </c>
       <c r="L31" t="n">
         <v>5.41</v>
@@ -2208,7 +2579,7 @@
         <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.86</v>
+        <v>3.76</v>
       </c>
       <c r="O31" t="n">
         <v>-1.75</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.96</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H32" t="n">
-        <v>120.9</v>
+        <v>116.13</v>
       </c>
       <c r="I32" t="n">
         <v>117.2043363681373</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.41</v>
+        <v>-4.34</v>
       </c>
       <c r="L32" t="n">
-        <v>3.78</v>
+        <v>4.87</v>
       </c>
       <c r="M32" t="n">
         <v>0.03</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.81</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H33" t="n">
-        <v>98.48999999999999</v>
+        <v>100.26</v>
       </c>
       <c r="I33" t="n">
         <v>99.87041443266277</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>15.19</v>
+        <v>13.67</v>
       </c>
       <c r="L33" t="n">
         <v>6.69</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.88</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H34" t="n">
-        <v>100.19</v>
+        <v>98.86</v>
       </c>
       <c r="I34" t="n">
         <v>99.34809790248666</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H35" t="n">
-        <v>97.63</v>
+        <v>100.44</v>
       </c>
       <c r="I35" t="n">
         <v>100.1846942881424</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K35" t="n">
-        <v>1.24</v>
+        <v>-1.6</v>
       </c>
       <c r="L35" t="n">
         <v>2.25</v>
@@ -2436,7 +2855,7 @@
         <v>1.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="O35" t="n">
         <v>-1.33</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.23</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="H36" t="n">
-        <v>98.67</v>
+        <v>92.5</v>
       </c>
       <c r="I36" t="n">
         <v>93.9965637500338</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.76</v>
+        <v>-7.91</v>
       </c>
       <c r="L36" t="n">
-        <v>2.92</v>
+        <v>8.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.12</v>
+        <v>4.73</v>
       </c>
       <c r="N36" t="n">
-        <v>2.21</v>
+        <v>6.25</v>
       </c>
       <c r="O36" t="n">
         <v>2.88</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H37" t="n">
-        <v>78.90000000000001</v>
+        <v>80.25</v>
       </c>
       <c r="I37" t="n">
         <v>79.90945152021099</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K37" t="n">
-        <v>14.7</v>
+        <v>13.24</v>
       </c>
       <c r="L37" t="n">
         <v>2.43</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2610,6 +3065,14 @@
       <c r="Q38" t="n">
         <v>8</v>
       </c>
+      <c r="R38" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5120,7 +5583,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="6">
@@ -5130,7 +5593,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="7">
@@ -5140,7 +5603,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -5150,7 +5613,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -5160,7 +5623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.2</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="10">
@@ -5170,7 +5633,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="11">
@@ -5210,7 +5673,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.76</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -5220,7 +5683,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.18</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="16">
@@ -5230,7 +5693,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.33</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -5240,7 +5703,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>444.07</v>
+        <v>370.62</v>
       </c>
     </row>
     <row r="18">
@@ -5250,7 +5713,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.8</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="19">
@@ -5260,7 +5723,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.25</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="20">
@@ -5270,7 +5733,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.4</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="21">
@@ -5290,7 +5753,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -5310,7 +5773,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5330,7 +5793,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.65</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="27">
@@ -5350,7 +5813,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
